--- a/data/trans_bre/P16A02-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A02-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,49; 14,0</t>
+          <t>5,85; 14,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,59; 15,7</t>
+          <t>4,6; 15,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 10,88</t>
+          <t>0,2; 10,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 15,96</t>
+          <t>1,15; 17,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,46; 224,24</t>
+          <t>57,66; 229,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,78; 153,21</t>
+          <t>31,22; 161,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 117,95</t>
+          <t>1,35; 107,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 223,23</t>
+          <t>4,47; 245,97</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 9,62</t>
+          <t>2,78; 9,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,3; 13,82</t>
+          <t>5,05; 14,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 11,14</t>
+          <t>1,78; 11,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 7,38</t>
+          <t>-9,04; 6,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,85; 126,47</t>
+          <t>28,53; 134,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,03; 109,01</t>
+          <t>29,75; 115,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,01; 76,64</t>
+          <t>8,45; 78,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-37,71; 46,72</t>
+          <t>-41,31; 39,22</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 11,2</t>
+          <t>2,75; 11,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,83; 20,72</t>
+          <t>11,64; 20,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 11,59</t>
+          <t>1,96; 10,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,02; 17,18</t>
+          <t>6,7; 16,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,5; 93,56</t>
+          <t>17,04; 98,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>70,92; 169,19</t>
+          <t>66,85; 157,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,17; 76,2</t>
+          <t>9,87; 73,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31,35; 106,76</t>
+          <t>30,24; 101,14</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 13,58</t>
+          <t>4,0; 13,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,47; 20,65</t>
+          <t>10,61; 20,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,92; 14,69</t>
+          <t>5,07; 14,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,78; 30,08</t>
+          <t>9,69; 30,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,08; 104,66</t>
+          <t>22,28; 106,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,79; 141,65</t>
+          <t>56,22; 144,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,64; 84,11</t>
+          <t>22,29; 85,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,73; 378,83</t>
+          <t>37,12; 324,38</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 12,46</t>
+          <t>0,98; 12,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,32; 20,29</t>
+          <t>7,67; 20,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,94; 23,67</t>
+          <t>10,23; 23,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,54; 19,16</t>
+          <t>9,27; 18,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 64,96</t>
+          <t>4,07; 68,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,27; 107,23</t>
+          <t>29,6; 105,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,71; 118,79</t>
+          <t>40,93; 119,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,3; 69,2</t>
+          <t>27,1; 67,68</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,62; 22,36</t>
+          <t>9,07; 22,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,66; 26,4</t>
+          <t>11,43; 27,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,76; 31,74</t>
+          <t>18,4; 32,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,48; 60,36</t>
+          <t>23,34; 59,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>49,97; 170,12</t>
+          <t>45,36; 169,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33,81; 115,86</t>
+          <t>35,74; 120,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>86,22; 217,55</t>
+          <t>83,36; 218,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>82,4; 252,41</t>
+          <t>81,09; 261,78</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,28; 23,36</t>
+          <t>6,75; 22,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,32; 29,71</t>
+          <t>14,17; 30,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,28; 24,78</t>
+          <t>9,74; 24,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21,08; 32,84</t>
+          <t>21,34; 32,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,31; 106,89</t>
+          <t>21,13; 103,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,8; 112,11</t>
+          <t>38,74; 116,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,13; 89,45</t>
+          <t>27,25; 86,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>47,07; 89,98</t>
+          <t>48,98; 91,43</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,06; 11,95</t>
+          <t>8,02; 11,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,31; 17,91</t>
+          <t>13,61; 17,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,1; 14,26</t>
+          <t>10,29; 14,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,55; 31,22</t>
+          <t>14,13; 30,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>54,56; 92,27</t>
+          <t>54,04; 91,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>70,06; 106,99</t>
+          <t>72,17; 104,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,19; 80,58</t>
+          <t>51,84; 80,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>60,43; 160,11</t>
+          <t>58,09; 154,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A02-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A02-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,43</t>
+          <t>8,96</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>76,6%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,85; 14,59</t>
+          <t>5,6; 13,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,6; 15,44</t>
+          <t>5,72; 15,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 10,2</t>
+          <t>0,4; 10,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 17,12</t>
+          <t>1,82; 17,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>57,66; 229,9</t>
+          <t>57,78; 219,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,22; 161,58</t>
+          <t>38,46; 167,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 107,99</t>
+          <t>1,99; 109,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,47; 245,97</t>
+          <t>11,37; 217,73</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>2,16</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 9,74</t>
+          <t>2,28; 9,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,05; 14,46</t>
+          <t>5,23; 14,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 11,4</t>
+          <t>2,51; 11,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 6,59</t>
+          <t>-3,65; 8,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,53; 134,79</t>
+          <t>21,87; 125,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,75; 115,21</t>
+          <t>31,28; 112,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,45; 78,24</t>
+          <t>12,77; 82,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,31; 39,22</t>
+          <t>-16,38; 58,67</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,88</t>
+          <t>12,44</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>69,17%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 11,42</t>
+          <t>3,26; 11,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,64; 20,03</t>
+          <t>11,8; 20,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 10,95</t>
+          <t>2,13; 10,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,7; 16,53</t>
+          <t>7,71; 16,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,04; 98,02</t>
+          <t>20,3; 97,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,85; 157,84</t>
+          <t>69,82; 167,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,87; 73,72</t>
+          <t>10,83; 68,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,24; 101,14</t>
+          <t>37,43; 108,66</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18,32</t>
+          <t>12,5</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>49,78%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,0; 13,58</t>
+          <t>4,17; 13,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,61; 20,64</t>
+          <t>10,36; 20,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 14,39</t>
+          <t>4,84; 14,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,69; 30,36</t>
+          <t>8,19; 17,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,28; 106,47</t>
+          <t>23,27; 113,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,22; 144,02</t>
+          <t>52,41; 138,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,29; 85,77</t>
+          <t>22,12; 85,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,12; 324,38</t>
+          <t>30,05; 75,2</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14,14</t>
+          <t>14,35</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>47,94%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 12,68</t>
+          <t>0,74; 12,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,67; 20,31</t>
+          <t>6,9; 19,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,23; 23,06</t>
+          <t>10,14; 23,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,27; 18,79</t>
+          <t>10,04; 19,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 68,91</t>
+          <t>2,28; 66,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,6; 105,04</t>
+          <t>27,23; 103,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,93; 119,27</t>
+          <t>39,05; 122,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,1; 67,68</t>
+          <t>30,6; 70,72</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41,16</t>
+          <t>25,67</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>149,64%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,07; 22,46</t>
+          <t>9,3; 21,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,43; 27,02</t>
+          <t>12,05; 26,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,4; 32,06</t>
+          <t>17,96; 31,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,34; 59,89</t>
+          <t>20,75; 30,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45,36; 169,21</t>
+          <t>46,55; 160,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,74; 120,83</t>
+          <t>36,7; 114,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>83,36; 218,87</t>
+          <t>86,16; 224,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>81,09; 261,78</t>
+          <t>68,21; 128,16</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26,94</t>
+          <t>26,89</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,7%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,75; 22,76</t>
+          <t>7,6; 23,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,17; 30,35</t>
+          <t>13,48; 29,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,74; 24,79</t>
+          <t>8,5; 24,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21,34; 32,62</t>
+          <t>21,19; 32,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,13; 103,48</t>
+          <t>24,75; 105,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,74; 116,42</t>
+          <t>37,04; 112,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,25; 86,79</t>
+          <t>22,71; 83,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>48,98; 91,43</t>
+          <t>48,61; 92,86</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19,49</t>
+          <t>15,2</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>63,99%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,02; 11,84</t>
+          <t>7,95; 11,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,61; 17,67</t>
+          <t>13,39; 17,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,29; 14,47</t>
+          <t>10,18; 14,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,13; 30,31</t>
+          <t>13,22; 17,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>54,04; 91,16</t>
+          <t>54,29; 88,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>72,17; 104,2</t>
+          <t>71,9; 104,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,84; 80,0</t>
+          <t>51,61; 81,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>58,09; 154,29</t>
+          <t>52,97; 76,03</t>
         </is>
       </c>
     </row>
